--- a/bilhetes.xlsx
+++ b/bilhetes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\confe\Dropbox\4 - catering\2026\Nacional Velocidade\ticket-system\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8386D85-D23E-4755-B9C6-0D5C66D769FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B86CD47-75A9-44BD-A7E0-C09A3E6FB513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-165" yWindow="-165" windowWidth="38730" windowHeight="21210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="6">
   <si>
     <t>nome</t>
   </si>
@@ -408,93 +408,325 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B3" s="2"/>
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B4" s="2"/>
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B5" s="2"/>
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B6" s="2"/>
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B7" s="2"/>
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B8" s="2"/>
+      <c r="A8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B9" s="2"/>
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B10" s="2"/>
+      <c r="A10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B11" s="2"/>
+      <c r="A11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B12" s="2"/>
+      <c r="A12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B13" s="2"/>
+      <c r="A13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B14" s="2"/>
+      <c r="A14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B15" s="2"/>
+      <c r="A15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B16" s="2"/>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B17" s="2"/>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B18" s="2"/>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B19" s="2"/>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B20" s="2"/>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B21" s="2"/>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B22" s="2"/>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B23" s="2"/>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B24" s="2"/>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B25" s="2"/>
-    </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B26" s="2"/>
-    </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B27" s="2"/>
-    </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B28" s="2"/>
-    </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B29" s="2"/>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B30" s="2"/>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B31" s="2"/>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B32" s="2"/>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.35">
@@ -1967,6 +2199,35 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{1132E869-DECA-421E-AF58-A3549AABC7AE}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{95C906D1-B73A-4F12-A115-F6A860D10948}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{56B07F5C-FE4A-4B6E-845B-93666E2E5764}"/>
+    <hyperlink ref="B5" r:id="rId4" xr:uid="{FCCE78EB-0FA1-4950-B095-E17E9290A1E7}"/>
+    <hyperlink ref="B6" r:id="rId5" xr:uid="{97626EB2-FFD3-4AC9-8FC4-79F8ADA0EE92}"/>
+    <hyperlink ref="B7" r:id="rId6" xr:uid="{1AE0A1C4-9256-4B7F-995D-E93516D068A2}"/>
+    <hyperlink ref="B8" r:id="rId7" xr:uid="{E8ECDAAC-B5C2-4A7E-9BB7-6B0F61A4B65A}"/>
+    <hyperlink ref="B9" r:id="rId8" xr:uid="{86A5FBD1-25A7-407C-A8CD-A54653A49C91}"/>
+    <hyperlink ref="B10" r:id="rId9" xr:uid="{3F65CF7A-42E5-4052-AD35-EDDC68FE58BB}"/>
+    <hyperlink ref="B11" r:id="rId10" xr:uid="{A18B9725-9E8A-4D48-BA32-01395155BF82}"/>
+    <hyperlink ref="B12" r:id="rId11" xr:uid="{BB69E05C-7600-483A-AEEA-E2D4F7D0EEA2}"/>
+    <hyperlink ref="B13" r:id="rId12" xr:uid="{7399F146-9650-433E-BF29-B8B65212C589}"/>
+    <hyperlink ref="B14" r:id="rId13" xr:uid="{DDB2465E-5095-446E-8506-AAB3E5CF6EFB}"/>
+    <hyperlink ref="B15" r:id="rId14" xr:uid="{96E1C7FC-AD7E-4259-A08E-339F42A49881}"/>
+    <hyperlink ref="B16" r:id="rId15" xr:uid="{3142178D-7354-460F-A582-455448D14EF9}"/>
+    <hyperlink ref="B17" r:id="rId16" xr:uid="{8273C382-3547-4482-A1C0-AC9AA0AA2C25}"/>
+    <hyperlink ref="B18" r:id="rId17" xr:uid="{64B54EA2-9BCE-4304-B433-8DEA4770AD21}"/>
+    <hyperlink ref="B19" r:id="rId18" xr:uid="{CAB28C14-2190-4D72-A7CC-D0E6A40C3BA7}"/>
+    <hyperlink ref="B20" r:id="rId19" xr:uid="{9C896BFF-3B04-453E-9ECF-A36A6EFF5086}"/>
+    <hyperlink ref="B21" r:id="rId20" xr:uid="{A9AC3712-3845-4E3E-B6B3-764F46B389F9}"/>
+    <hyperlink ref="B22" r:id="rId21" xr:uid="{D712E83D-9ACA-4BBE-AB37-81B7878A153F}"/>
+    <hyperlink ref="B23" r:id="rId22" xr:uid="{A36FC995-CC59-43EF-A6C8-3C6314DB599B}"/>
+    <hyperlink ref="B24" r:id="rId23" xr:uid="{DC3515E1-B0C2-47DA-B6CC-384A0A82BA3B}"/>
+    <hyperlink ref="B25" r:id="rId24" xr:uid="{B3C6BDCD-33A4-4ED6-9C8E-D38899A460E4}"/>
+    <hyperlink ref="B26" r:id="rId25" xr:uid="{47F7B7DE-6AC7-40B9-B5BC-D260B2587521}"/>
+    <hyperlink ref="B27" r:id="rId26" xr:uid="{B5685AC4-3F7B-40FB-A251-181087E6CEDD}"/>
+    <hyperlink ref="B28" r:id="rId27" xr:uid="{C2711318-1028-4B28-A3C8-D696E5682154}"/>
+    <hyperlink ref="B29" r:id="rId28" xr:uid="{F8ABB3A1-5C28-401E-89A4-A202262DEABB}"/>
+    <hyperlink ref="B30" r:id="rId29" xr:uid="{0827E09B-9018-4A8D-AB09-1C2A766CFDBC}"/>
+    <hyperlink ref="B31" r:id="rId30" xr:uid="{A03390BB-4EBA-45E9-B980-51E897D3C75C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
